--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,48 +1444,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118372095</v>
+        <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>93189</v>
+        <v>91924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbricka, Vstm</t>
+          <t>Karmansbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537557</v>
+        <v>537560</v>
       </c>
       <c r="R9" t="n">
-        <v>6615054</v>
+        <v>6614900</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,12 +1513,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2011-05-17</t>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,58 +1548,54 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118372095</t>
+          <t>https://artportalen.se/Sighting/137282812</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137007775</v>
+        <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>91924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1589,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537534</v>
+        <v>537529</v>
       </c>
       <c r="R10" t="n">
-        <v>6614886</v>
+        <v>6614997</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1619,22 +1634,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1665,16 +1680,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137007775</t>
+          <t>https://artportalen.se/Sighting/137282813</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118372092</v>
+        <v>118372095</v>
       </c>
       <c r="B11" t="n">
-        <v>93215</v>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,54 +1786,58 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118372092</t>
+          <t>https://artportalen.se/Sighting/118372095</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118372083</v>
+        <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valbricka, Vstm</t>
+          <t>Karmansbo, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537472</v>
+        <v>537534</v>
       </c>
       <c r="R12" t="n">
-        <v>6614904</v>
+        <v>6614886</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,12 +1861,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-05-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,31 +1896,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118372083</t>
+          <t>https://artportalen.se/Sighting/137007775</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137007692</v>
+        <v>118372092</v>
       </c>
       <c r="B13" t="n">
-        <v>93480</v>
+        <v>93215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,41 +1924,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karmansbo, Vstm</t>
+          <t>Valbricka, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537521</v>
+        <v>537557</v>
       </c>
       <c r="R13" t="n">
-        <v>6614913</v>
+        <v>6615054</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1952,27 +1978,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>08:44</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2011-05-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,69 +1998,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137007692</t>
+          <t>https://artportalen.se/Sighting/118372092</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137007693</v>
+        <v>118372083</v>
       </c>
       <c r="B14" t="n">
-        <v>93480</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Karmansbo, Vstm</t>
+          <t>Valbricka, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537509</v>
+        <v>537472</v>
       </c>
       <c r="R14" t="n">
-        <v>6614933</v>
+        <v>6614904</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,27 +2084,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:38</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2011-05-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2108,27 +2104,31 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137007693</t>
+          <t>https://artportalen.se/Sighting/118372083</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137007696</v>
+        <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2164,13 +2164,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537580</v>
+        <v>537521</v>
       </c>
       <c r="R15" t="n">
-        <v>6614914</v>
+        <v>6614913</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2194,22 +2194,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2240,54 +2240,58 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137007696</t>
+          <t>https://artportalen.se/Sighting/137007692</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118372120</v>
+        <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbricka, Vstm</t>
+          <t>Karmansbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537616</v>
+        <v>537509</v>
       </c>
       <c r="R16" t="n">
-        <v>6615046</v>
+        <v>6614933</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2311,12 +2315,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2011-05-17</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2331,69 +2350,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118372120</t>
+          <t>https://artportalen.se/Sighting/137007693</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118372121</v>
+        <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>93483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbricka, Vstm</t>
+          <t>Karmansbo, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537589</v>
+        <v>537580</v>
       </c>
       <c r="R17" t="n">
-        <v>6615054</v>
+        <v>6614914</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2417,12 +2436,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2011-05-16</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2011-05-17</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,31 +2471,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118372121</t>
+          <t>https://artportalen.se/Sighting/137007696</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96308115</v>
+        <v>118372120</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,42 +2499,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>sluttning Abborrtjärnen, Vstm</t>
+          <t>Valbricka, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537496</v>
+        <v>537616</v>
       </c>
       <c r="R18" t="n">
-        <v>6614937</v>
+        <v>6615046</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2531,27 +2553,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer som ett ringlande stråk i den djupa mossmattan längs sidan av höjden. Många överblommade blomstänglar. Äldre barrskog.</t>
+          <t>2011-05-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,34 +2567,37 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annika Holmström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annika Holmström</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96308115</t>
+          <t>https://artportalen.se/Sighting/118372120</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97260839</v>
+        <v>118372121</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,43 +2605,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, sydsluttning (knärot), Vstm</t>
+          <t>Valbricka, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537495</v>
+        <v>537589</v>
       </c>
       <c r="R19" t="n">
-        <v>6614937</v>
+        <v>6615054</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2656,24 +2657,14 @@
           <t>Västra Skedvi</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>U-Köp-0233</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
+          <t>2011-05-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>växer som ett ringlande stråki den djupa mossan längs sidan av höjden.Många överblommade stänglar</t>
+          <t>2011-05-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2684,82 +2675,81 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>äldre barrskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Annika Holmström</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97260839</t>
+          <t>https://artportalen.se/Sighting/118372121</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137007675</v>
+        <v>96308115</v>
       </c>
       <c r="B20" t="n">
-        <v>98253</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Karmansbo, Vstm</t>
+          <t>sluttning Abborrtjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537649</v>
+        <v>537496</v>
       </c>
       <c r="R20" t="n">
-        <v>6614897</v>
+        <v>6614937</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,27 +2773,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Växer som ett ringlande stråk i den djupa mossmattan längs sidan av höjden. Många överblommade blomstänglar. Äldre barrskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,22 +2802,395 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Annika Holmström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Annika Holmström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96308115</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>97260839</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, sydsluttning (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>537495</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6614937</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Västra Skedvi</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>U-Köp-0233</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>växer som ett ringlande stråki den djupa mossan längs sidan av höjden.Många överblommade stänglar</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Holmström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97260839</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137282883</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99394</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Karmansbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>537488</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6614956</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Västra Skedvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282883</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137007675</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Karmansbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>537649</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6614897</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Västra Skedvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137007675</t>
         </is>
@@ -2854,6 +3217,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 42857-2026 artfynd.xlsx
+++ b/artfynd/A 42857-2026 artfynd.xlsx
@@ -1447,7 +1447,7 @@
         <v>137282812</v>
       </c>
       <c r="B9" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137282813</v>
       </c>
       <c r="B10" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>137007775</v>
       </c>
       <c r="B12" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137007692</v>
       </c>
       <c r="B15" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>137007693</v>
       </c>
       <c r="B16" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>137007696</v>
       </c>
       <c r="B17" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137282883</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>137007675</v>
       </c>
       <c r="B23" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
